--- a/models/3_Statement_Model.xlsx
+++ b/models/3_Statement_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cb10f4a09bcef627/Documents/GitHub/XD_Grad_Portfolio/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="124" documentId="8_{2465401F-8E98-4D2A-899A-91CC703B4779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E58B170-3C1C-499B-9B81-7CB4087DB9EE}"/>
+  <xr:revisionPtr revIDLastSave="126" documentId="8_{2465401F-8E98-4D2A-899A-91CC703B4779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E172D60-1773-42C0-917D-57125F198DE7}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Income Statement" sheetId="5" r:id="rId1"/>
@@ -62,6 +62,31 @@
     <author>Xavier Davis</author>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{7C8C93A0-0C67-4E10-A121-6256B2237764}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Xavier Davis:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+this is a test note 
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="N3" authorId="0" shapeId="0" xr:uid="{8327D9A4-E1D3-4F76-86F6-50FE5489AA85}">
       <text>
         <r>
@@ -455,7 +480,7 @@
     <numFmt numFmtId="173" formatCode="[Color10]0.00%;[Red]\(0.00\)%;\-"/>
     <numFmt numFmtId="174" formatCode="0;\(0\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -523,6 +548,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="7">

--- a/models/3_Statement_Model.xlsx
+++ b/models/3_Statement_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cb10f4a09bcef627/Documents/GitHub/XD_Grad_Portfolio/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="126" documentId="8_{2465401F-8E98-4D2A-899A-91CC703B4779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E172D60-1773-42C0-917D-57125F198DE7}"/>
+  <xr:revisionPtr revIDLastSave="127" documentId="8_{2465401F-8E98-4D2A-899A-91CC703B4779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B27CC0B-451F-47F4-B368-A6A98E58086E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="3276" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Income Statement" sheetId="5" r:id="rId1"/>
@@ -62,31 +62,6 @@
     <author>Xavier Davis</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{7C8C93A0-0C67-4E10-A121-6256B2237764}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Xavier Davis:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-this is a test note 
-</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="N3" authorId="0" shapeId="0" xr:uid="{8327D9A4-E1D3-4F76-86F6-50FE5489AA85}">
       <text>
         <r>
@@ -480,7 +455,7 @@
     <numFmt numFmtId="173" formatCode="[Color10]0.00%;[Red]\(0.00\)%;\-"/>
     <numFmt numFmtId="174" formatCode="0;\(0\)"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -548,19 +523,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="7">

--- a/models/3_Statement_Model.xlsx
+++ b/models/3_Statement_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cb10f4a09bcef627/Documents/GitHub/XD_Grad_Portfolio/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="127" documentId="8_{2465401F-8E98-4D2A-899A-91CC703B4779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B27CC0B-451F-47F4-B368-A6A98E58086E}"/>
+  <xr:revisionPtr revIDLastSave="147" documentId="8_{2465401F-8E98-4D2A-899A-91CC703B4779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D3E599B-5F7D-4089-9ED4-37B5C6A560A2}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="3276" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Income Statement" sheetId="5" r:id="rId1"/>
@@ -1101,7 +1101,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="11" width="14.6640625" customWidth="1"/>
+    <col min="2" max="2" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="11" width="14.6640625" customWidth="1"/>
     <col min="13" max="13" width="24.21875" bestFit="1" customWidth="1"/>
     <col min="14" max="24" width="14.6640625" customWidth="1"/>
   </cols>
@@ -1111,12 +1112,15 @@
         <v>1</v>
       </c>
       <c r="B1" s="2">
+        <f>YEAR(DATEVALUE("JAN-2020"))</f>
         <v>2020</v>
       </c>
       <c r="C1" s="2">
+        <f>YEAR(DATEVALUE("JAN-2021"))</f>
         <v>2021</v>
       </c>
       <c r="D1" s="2">
+        <f>YEAR(DATEVALUE("JAN-2022"))</f>
         <v>2022</v>
       </c>
       <c r="E1" s="2">

--- a/models/3_Statement_Model.xlsx
+++ b/models/3_Statement_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cb10f4a09bcef627/Documents/GitHub/XD_Grad_Portfolio/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="147" documentId="8_{2465401F-8E98-4D2A-899A-91CC703B4779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D3E599B-5F7D-4089-9ED4-37B5C6A560A2}"/>
+  <xr:revisionPtr revIDLastSave="163" documentId="8_{2465401F-8E98-4D2A-899A-91CC703B4779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF99FA99-3C6E-4D2E-8FB6-3A867BEF028C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Income Statement" sheetId="5" r:id="rId1"/>
@@ -749,7 +749,21 @@
     <cellStyle name="Note" xfId="2" builtinId="10"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF3F4F6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF3F4F6"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1124,24 +1138,31 @@
         <v>2022</v>
       </c>
       <c r="E1" s="2">
+        <f>YEAR(DATEVALUE("JAN-2023"))</f>
         <v>2023</v>
       </c>
       <c r="F1" s="2">
+        <f>YEAR(DATEVALUE("JAN-2024"))</f>
         <v>2024</v>
       </c>
       <c r="G1" s="20">
+        <f>YEAR(DATEVALUE("JAN-2025"))</f>
         <v>2025</v>
       </c>
       <c r="H1" s="20">
+        <f>YEAR(DATEVALUE("JAN-2026"))</f>
         <v>2026</v>
       </c>
       <c r="I1" s="20">
+        <f>YEAR(DATEVALUE("JAN-2027"))</f>
         <v>2027</v>
       </c>
       <c r="J1" s="20">
+        <f>YEAR(DATEVALUE("JAN-2028"))</f>
         <v>2028</v>
       </c>
       <c r="K1" s="20">
+        <f>YEAR(DATEVALUE("JAN-2029"))</f>
         <v>2029</v>
       </c>
     </row>
@@ -2844,17 +2865,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G1:K21">
-    <cfRule type="notContainsErrors" dxfId="5" priority="3">
+    <cfRule type="notContainsErrors" dxfId="7" priority="3">
       <formula>NOT(ISERROR(G1))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G23:K25 G27:K27 G30:K31">
-    <cfRule type="notContainsErrors" dxfId="4" priority="8">
+    <cfRule type="notContainsErrors" dxfId="6" priority="8">
       <formula>NOT(ISERROR(G23))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G37:K46">
-    <cfRule type="notContainsErrors" dxfId="3" priority="1">
+    <cfRule type="notContainsErrors" dxfId="5" priority="1">
       <formula>NOT(ISERROR(G37))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2883,33 +2904,43 @@
         <v>1</v>
       </c>
       <c r="B1" s="2">
+        <f>YEAR(DATEVALUE("JAN-2020"))</f>
         <v>2020</v>
       </c>
       <c r="C1" s="2">
+        <f>YEAR(DATEVALUE("JAN-2021"))</f>
         <v>2021</v>
       </c>
       <c r="D1" s="2">
+        <f>YEAR(DATEVALUE("JAN-2022"))</f>
         <v>2022</v>
       </c>
       <c r="E1" s="2">
+        <f>YEAR(DATEVALUE("JAN-2023"))</f>
         <v>2023</v>
       </c>
       <c r="F1" s="2">
+        <f>YEAR(DATEVALUE("JAN-2024"))</f>
         <v>2024</v>
       </c>
       <c r="G1" s="20">
+        <f>YEAR(DATEVALUE("JAN-2025"))</f>
         <v>2025</v>
       </c>
       <c r="H1" s="20">
+        <f>YEAR(DATEVALUE("JAN-2026"))</f>
         <v>2026</v>
       </c>
       <c r="I1" s="20">
+        <f>YEAR(DATEVALUE("JAN-2027"))</f>
         <v>2027</v>
       </c>
       <c r="J1" s="20">
+        <f>YEAR(DATEVALUE("JAN-2028"))</f>
         <v>2028</v>
       </c>
       <c r="K1" s="20">
+        <f>YEAR(DATEVALUE("JAN-2029"))</f>
         <v>2029</v>
       </c>
       <c r="M1" t="s">
@@ -7527,14 +7558,19 @@
       <c r="M216" s="10"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G1:K21">
-    <cfRule type="notContainsErrors" dxfId="2" priority="1">
-      <formula>NOT(ISERROR(G1))</formula>
+  <conditionalFormatting sqref="G2:K21">
+    <cfRule type="notContainsErrors" dxfId="4" priority="2">
+      <formula>NOT(ISERROR(G2))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G23:K45">
-    <cfRule type="notContainsErrors" dxfId="1" priority="6">
+    <cfRule type="notContainsErrors" dxfId="3" priority="7">
       <formula>NOT(ISERROR(G23))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:K1">
+    <cfRule type="notContainsErrors" dxfId="1" priority="1">
+      <formula>NOT(ISERROR(G1))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7564,18 +7600,23 @@
         <v>1</v>
       </c>
       <c r="B1" s="20">
+        <f>YEAR(DATEVALUE("JAN-2025"))</f>
         <v>2025</v>
       </c>
       <c r="C1" s="20">
+        <f>YEAR(DATEVALUE("JAN-2026"))</f>
         <v>2026</v>
       </c>
       <c r="D1" s="20">
+        <f>YEAR(DATEVALUE("JAN-2027"))</f>
         <v>2027</v>
       </c>
       <c r="E1" s="20">
+        <f>YEAR(DATEVALUE("JAN-2028"))</f>
         <v>2028</v>
       </c>
       <c r="F1" s="20">
+        <f>YEAR(DATEVALUE("JAN-2029"))</f>
         <v>2029</v>
       </c>
     </row>
@@ -10036,7 +10077,12 @@
       <c r="H214" s="10"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B1:F45">
+  <conditionalFormatting sqref="B2:F45">
+    <cfRule type="notContainsErrors" dxfId="2" priority="2">
+      <formula>NOT(ISERROR(B2))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:F1">
     <cfRule type="notContainsErrors" dxfId="0" priority="1">
       <formula>NOT(ISERROR(B1))</formula>
     </cfRule>
